--- a/Outputs/Scenarios/PtX_demand_LT_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LT_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.003207264563663378</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001908980623117159</v>
+        <v>0.002073255167090504</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.003181634371861933</v>
+        <v>0.003003009503643353</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>4.62112533740057e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001272653748744773</v>
+        <v>0.001287004072990009</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.004747964713591852</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01030217745566235</v>
+        <v>0.01118871631465711</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01717029575943724</v>
+        <v>0.01620631264295216</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0002498928796627291</v>
       </c>
       <c r="K42" t="n">
-        <v>0.006868118303774898</v>
+        <v>0.006945562561265214</v>
       </c>
     </row>
     <row r="43">
